--- a/backend/data/rule_sets/correction_general_1783409223_81a47f/source.xlsx
+++ b/backend/data/rule_sets/correction_general_1783409223_81a47f/source.xlsx
@@ -2514,7 +2514,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"财产来源","op":"contains_any","values":["财产权"]},"target":{"field":"产品基本信息.是否信托受益权转让","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"产品基本信息.财产来源","op":"contains","value":"财产权"},"target":{"field":"产品基本信息.是否信托受益权转让","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2550,7 +2550,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2802,7 +2806,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"是否信托受益权转让","op":"equals","value":"拆分转让"},"target":{"field":"产品基本信息.发行、转让场所","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"产品基本信息.是否信托受益权转让","op":"contains_any","values":["拆分转让","整体转让"]},"target":{"field":"产品基本信息.发行、转让场所","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2838,7 +2842,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2992,7 +3000,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"发行、转让场所","op":"equals","value":"其他"},"target":{"field":"产品基本信息.发行、转让场所补充说明","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"产品基本信息.发行、转让场所","op":"equals","value":"其他"},"target":{"field":"产品基本信息.发行、转让场所补充说明","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3028,7 +3036,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -3567,7 +3579,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"开放频度","op":"equals","value":"其他"},"target":{"field":"产品基本信息.开放频度补充说明","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"产品基本信息.开放频度","op":"equals","value":"其他"},"target":{"field":"产品基本信息.开放频度补充说明","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3603,7 +3615,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3758,7 +3774,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"equals","value":"资产管理信托"},"target":{"field":"产品基本信息.是否为结构化信托","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"资产管理信托"},"target":{"field":"产品基本信息.是否为结构化信托","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -3794,7 +3810,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3948,7 +3968,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"是否为结构化信托","op":"equals","value":"是"},"target":{"field":"产品基本信息.约定优先劣后受益权比例","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"产品基本信息.是否为结构化信托","op":"equals","value":"是"},"target":{"field":"产品基本信息.约定优先劣后受益权比例","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -3984,7 +4004,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -4328,7 +4352,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"logic":"AND","conditions":[{"field":"信托业务分类","op":"equals","value":"资产管理信托"},{"field":"项目运作模式","op":"equals","value":"封闭式"}]},"target":{"field":"产品基本信息.是否分期募集放款","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"logic":"AND","conditions":[{"field":"业务分类信息.信托业务分类","op":"equals","value":"资产管理信托"},{"field":"产品基本信息.项目运作模式","op":"equals","value":"封闭式"}]},"target":{"field":"产品基本信息.是否分期募集放款","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4364,7 +4388,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -4994,7 +5022,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"equals","value":"资产管理信托"},"target":{"field":"业务分类信息.资产管理信托分类","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"资产管理信托"},"target":{"field":"业务分类信息.资产管理信托分类","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5030,7 +5058,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -5189,7 +5221,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"equals","value":"资产服务信托"},"target":{"field":"业务分类信息.资产服务信托分类1","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"资产服务信托"},"target":{"field":"业务分类信息.资产服务信托分类1","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5225,7 +5257,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -5388,7 +5424,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"equals","value":"资产服务信托"},"target":{"field":"业务分类信息.资产服务信托分类2","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"资产服务信托"},"target":{"field":"业务分类信息.资产服务信托分类2","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -5424,7 +5460,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -5580,7 +5620,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"equals","value":"公益慈善信托"},"target":{"field":"业务分类信息.公益慈善信托分类","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"公益慈善信托"},"target":{"field":"业务分类信息.公益慈善信托分类","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -5616,7 +5656,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -5771,7 +5815,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"equals","value":"公益慈善信托"},"target":{"field":"业务分类信息.是否在民政部门备案","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"公益慈善信托"},"target":{"field":"业务分类信息.是否在民政部门备案","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -5807,7 +5851,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -5961,7 +6009,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"equals","value":"待整改业务"},"target":{"field":"业务分类信息.待整改原因","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"待整改业务"},"target":{"field":"业务分类信息.待整改原因","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -5997,7 +6045,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -6151,7 +6203,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"equals","value":"待整改业务"},"target":{"field":"业务分类信息.整改计划","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"待整改业务"},"target":{"field":"业务分类信息.整改计划","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -6187,7 +6239,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -6341,7 +6397,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"equals","value":"待整改业务"},"target":{"field":"业务分类信息.计划完成整改时间","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"待整改业务"},"target":{"field":"业务分类信息.计划完成整改时间","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -6377,7 +6433,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -6532,7 +6592,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"contains_any","values":["资产管理信托","待整改业务"]},"target":{"field":"业务分类信息.是否以管理契约型私募基金形式开展资产管理信托","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"contains_any","values":["资产管理信托","待整改业务"]},"target":{"field":"业务分类信息.是否以管理契约型私募基金形式开展资产管理信托","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -6568,7 +6628,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -6723,7 +6787,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"业务分类信息.是否金融通道业务","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"业务分类信息.是否金融通道业务","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -6759,7 +6823,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -6914,7 +6982,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"业务分类信息.是否为融资方服务的私募投行业务","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"业务分类信息.是否为融资方服务的私募投行业务","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -6950,7 +7018,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -7105,7 +7177,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"equals","value":"资产服务信托"},"target":{"field":"业务分类信息.是否参与资金募集","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"资产服务信托"},"target":{"field":"业务分类信息.是否参与资金募集","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -7141,7 +7213,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -7296,7 +7372,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"contains_any","values":["资产管理信托","待整改业务"]},"target":{"field":"业务分类信息.是否满足非公开发行要求","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"contains_any","values":["资产管理信托","待整改业务"]},"target":{"field":"业务分类信息.是否满足非公开发行要求","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -7332,7 +7408,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -7580,7 +7660,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"产品特征.是否互联网贷款","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"产品特征.是否互联网贷款","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -7616,7 +7696,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -7775,7 +7859,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"是否互联网贷款","op":"equals","value":"是"},"target":{"field":"产品特征.业务模式","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"产品特征.是否互联网贷款","op":"equals","value":"是"},"target":{"field":"产品特征.业务模式","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -7811,7 +7895,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -7966,7 +8054,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"产品特征.是否证券投资类信托","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"产品特征.是否证券投资类信托","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -8002,7 +8090,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -8157,7 +8249,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"产品特征.是否受托境外理财信托（QDII）","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"产品特征.是否受托境外理财信托（QDII）","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -8193,7 +8285,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -8539,7 +8635,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"是否绿色信托","op":"equals","value":"是"},"target":{"field":"产品特征.绿色信托业务模式","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"产品特征.是否绿色信托","op":"equals","value":"是"},"target":{"field":"产品特征.绿色信托业务模式","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
@@ -8575,7 +8671,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -8729,7 +8829,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"产品特征.是否城市更新","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"产品特征.是否城市更新","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -8765,7 +8865,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -9296,7 +9400,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"产品特征.是否资产证券双SPV结构下的资产层信托","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"contains_any","values":["资产管理信托","资产服务信托","待整改业务"]},"target":{"field":"产品特征.是否资产证券双SPV结构下的资产层信托","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -9332,7 +9436,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -12937,7 +13045,7 @@
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"equals","value":"资产管理信托"},"target":{"field":"初始信托规模.募集起始日期","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"资产管理信托"},"target":{"field":"初始信托规模.募集起始日期","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N131" s="2" t="inlineStr">
@@ -12973,7 +13081,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U131" s="2" t="inlineStr"/>
+      <c r="U131" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -13127,7 +13239,7 @@
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"信托业务分类","op":"equals","value":"资产管理信托"},"target":{"field":"初始信托规模.募集结束日期","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"业务分类信息.信托业务分类","op":"equals","value":"资产管理信托"},"target":{"field":"初始信托规模.募集结束日期","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N133" s="2" t="inlineStr">
@@ -13163,7 +13275,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U133" s="2" t="inlineStr"/>
+      <c r="U133" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -13317,7 +13433,7 @@
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"期限类型","op":"equals","value":"固定期限"},"target":{"field":"初始信托规模.信托产品期限","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始信托规模.期限类型","op":"equals","value":"固定期限"},"target":{"field":"初始信托规模.信托产品期限","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N135" s="2" t="inlineStr">
@@ -13353,7 +13469,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U135" s="2" t="inlineStr"/>
+      <c r="U135" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -15698,7 +15818,7 @@
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"委托人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始委托人及其财产信息.管理人名称","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始委托人及其财产信息.委托人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始委托人及其财产信息.管理人名称","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
@@ -15734,7 +15854,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U160" s="2" t="inlineStr"/>
+      <c r="U160" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -15895,7 +16019,7 @@
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"委托人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始委托人及其财产信息.管理人证件类型","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始委托人及其财产信息.委托人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始委托人及其财产信息.管理人证件类型","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
@@ -15931,7 +16055,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U162" s="2" t="inlineStr"/>
+      <c r="U162" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -16085,7 +16213,7 @@
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"委托人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始委托人及其财产信息.管理人证件号码","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始委托人及其财产信息.委托人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始委托人及其财产信息.管理人证件号码","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
@@ -16121,7 +16249,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U164" s="2" t="inlineStr"/>
+      <c r="U164" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -16276,7 +16408,7 @@
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"委托人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始委托人及其财产信息.是否本公司发行产品","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始委托人及其财产信息.委托人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始委托人及其财产信息.是否本公司发行产品","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
@@ -16312,7 +16444,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U166" s="2" t="inlineStr"/>
+      <c r="U166" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -16466,7 +16602,7 @@
       </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"委托人类型","op":"contains_any","values":["非金融企业","金融机构（实体）"]},"target":{"field":"初始委托人及其财产信息.委托人是否上市","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始委托人及其财产信息.委托人类型","op":"contains_any","values":["非金融企业","金融机构（实体"]},"target":{"field":"初始委托人及其财产信息.委托人是否上市","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N168" s="2" t="inlineStr">
@@ -16502,7 +16638,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U168" s="2" t="inlineStr"/>
+      <c r="U168" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -16847,7 +16987,7 @@
       </c>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"委托资产类型","op":"contains_any","values":["其他"]},"target":{"field":"初始委托人及其财产信息.委托资产类型补充说明","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始委托人及其财产信息.委托资产类型","op":"contains","value":"其他"},"target":{"field":"初始委托人及其财产信息.委托资产类型补充说明","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
@@ -16883,7 +17023,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U172" s="2" t="inlineStr"/>
+      <c r="U172" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -18736,7 +18880,7 @@
       </c>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"受益人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始受益权信息.管理人名称","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始受益权信息.受益人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始受益权信息.管理人名称","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N192" s="2" t="inlineStr">
@@ -18772,7 +18916,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U192" s="2" t="inlineStr"/>
+      <c r="U192" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -18929,7 +19077,7 @@
       </c>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"受益人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始受益权信息.管理人证件类型","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始受益权信息.受益人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始受益权信息.管理人证件类型","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N194" s="2" t="inlineStr">
@@ -18965,7 +19113,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U194" s="2" t="inlineStr"/>
+      <c r="U194" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -19119,7 +19271,7 @@
       </c>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"受益人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始受益权信息.管理人证件号码","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始受益权信息.受益人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始受益权信息.管理人证件号码","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N196" s="2" t="inlineStr">
@@ -19155,7 +19307,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U196" s="2" t="inlineStr"/>
+      <c r="U196" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -19310,7 +19466,7 @@
       </c>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"受益人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始受益权信息.是否本公司发行产品","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始受益权信息.受益人类型","op":"equals","value":"特定目的载体"},"target":{"field":"初始受益权信息.是否本公司发行产品","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N198" s="2" t="inlineStr">
@@ -19346,7 +19502,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U198" s="2" t="inlineStr"/>
+      <c r="U198" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -19501,7 +19661,7 @@
       </c>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"受益人类型","op":"contains_any","values":["非金融企业","金融机构（实体）"]},"target":{"field":"初始受益权信息.受益人是否上市","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始受益权信息.受益人类型","op":"contains_any","values":["非金融企业","金融机构（实体"]},"target":{"field":"初始受益权信息.受益人是否上市","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N200" s="2" t="inlineStr">
@@ -19537,7 +19697,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U200" s="2" t="inlineStr"/>
+      <c r="U200" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -19970,7 +20134,7 @@
       </c>
       <c r="M205" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"运作模式","op":"equals","value":"封闭式净值型"},"target":{"field":"初始受益权信息.单位净值","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"运作模式","op":"contains_any","values":["封闭式净值型","开放式净值型"]},"target":{"field":"初始受益权信息.单位净值","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N205" s="2" t="inlineStr">
@@ -20006,7 +20170,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U205" s="2" t="inlineStr"/>
+      <c r="U205" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -20905,7 +21073,7 @@
       </c>
       <c r="M215" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"合同是否记载业绩比较基准","op":"equals","value":"是"},"target":{"field":"初始受益权信息.业绩比较基准（下限）","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始受益权信息.合同是否记载业绩比较基准","op":"equals","value":"是"},"target":{"field":"初始受益权信息.业绩比较基准（下限）","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N215" s="2" t="inlineStr">
@@ -20941,7 +21109,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U215" s="2" t="inlineStr"/>
+      <c r="U215" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -21095,7 +21267,7 @@
       </c>
       <c r="M217" s="2" t="inlineStr">
         <is>
-          <t>{"trigger":{"field":"合同是否记载业绩比较基准","op":"equals","value":"是"},"target":{"field":"初始受益权信息.业绩比较基准（上限）","op":"required"},"source_check_type":"条件性必填"}</t>
+          <t>{"trigger":{"field":"初始受益权信息.合同是否记载业绩比较基准","op":"equals","value":"是"},"target":{"field":"初始受益权信息.业绩比较基准（上限）","op":"required"},"source_check_type":"条件性必填"}</t>
         </is>
       </c>
       <c r="N217" s="2" t="inlineStr">
@@ -21131,7 +21303,11 @@
           <t>是</t>
         </is>
       </c>
-      <c r="U217" s="2" t="inlineStr"/>
+      <c r="U217" s="2" t="inlineStr">
+        <is>
+          <t>已修正：条件必填按trigger触发后检查required。</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
